--- a/data/trans_camb/IP18_E_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP18_E_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 1,43</t>
+          <t>-8,21; 1,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 1,35</t>
+          <t>-7,86; 1,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 4,12</t>
+          <t>-17,35; 3,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 8,93</t>
+          <t>0,85; 9,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 6,59</t>
+          <t>-2,65; 6,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 7,6</t>
+          <t>-5,29; 7,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 3,99</t>
+          <t>-2,06; 4,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 2,93</t>
+          <t>-3,56; 3,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 4,81</t>
+          <t>-6,18; 4,73</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 1,5</t>
+          <t>-8,33; 1,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 1,41</t>
+          <t>-8,0; 1,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,31; 4,34</t>
+          <t>-17,75; 3,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 9,92</t>
+          <t>0,85; 10,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 7,3</t>
+          <t>-2,75; 7,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 8,31</t>
+          <t>-5,5; 8,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 4,29</t>
+          <t>-2,13; 4,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 3,12</t>
+          <t>-3,71; 3,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 5,15</t>
+          <t>-6,45; 5,01</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 7,39</t>
+          <t>0,91; 7,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 4,35</t>
+          <t>-3,17; 4,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 2,97</t>
+          <t>-13,39; 3,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 4,23</t>
+          <t>-3,78; 4,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 6,21</t>
+          <t>-1,25; 5,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 6,86</t>
+          <t>-4,79; 6,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 4,82</t>
+          <t>-0,36; 5,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 4,0</t>
+          <t>-1,39; 3,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 3,72</t>
+          <t>-5,85; 3,55</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 8,16</t>
+          <t>0,94; 8,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 4,76</t>
+          <t>-3,31; 4,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 3,18</t>
+          <t>-13,99; 3,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 4,63</t>
+          <t>-3,95; 4,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 6,85</t>
+          <t>-1,3; 6,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 7,49</t>
+          <t>-5,08; 6,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 5,21</t>
+          <t>-0,37; 5,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 4,35</t>
+          <t>-1,44; 4,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 3,98</t>
+          <t>-6,14; 3,82</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 7,11</t>
+          <t>-2,89; 6,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 8,68</t>
+          <t>-1,06; 8,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-48,68; -2,69</t>
+          <t>-43,05; -3,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 5,88</t>
+          <t>-4,27; 5,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 8,11</t>
+          <t>-0,79; 8,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 7,86</t>
+          <t>-13,36; 7,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 5,5</t>
+          <t>-2,28; 4,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 6,92</t>
+          <t>0,2; 6,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-25,39; 0,31</t>
+          <t>-24,43; 0,43</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 8,23</t>
+          <t>-3,08; 7,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 9,86</t>
+          <t>-1,06; 9,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-53,05; -3,09</t>
+          <t>-47,49; -3,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 6,56</t>
+          <t>-4,51; 6,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 9,14</t>
+          <t>-0,83; 9,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 8,62</t>
+          <t>-14,36; 8,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 6,15</t>
+          <t>-2,44; 5,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,05; 7,84</t>
+          <t>0,28; 7,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-27,84; 0,39</t>
+          <t>-26,26; 0,57</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 4,52</t>
+          <t>-3,77; 4,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 5,03</t>
+          <t>-3,58; 4,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 0,13</t>
+          <t>-25,69; -1,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 6,1</t>
+          <t>-3,0; 5,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 2,02</t>
+          <t>-7,41; 1,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 4,67</t>
+          <t>-14,05; 5,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 4,17</t>
+          <t>-1,91; 4,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 2,17</t>
+          <t>-4,12; 2,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,55; -0,02</t>
+          <t>-14,94; 0,11</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 5,01</t>
+          <t>-3,91; 5,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 5,58</t>
+          <t>-3,76; 5,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-25,53; -0,14</t>
+          <t>-27,23; -1,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 6,72</t>
+          <t>-3,16; 6,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 2,23</t>
+          <t>-7,88; 2,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 5,13</t>
+          <t>-15,33; 6,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 4,56</t>
+          <t>-2,11; 4,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 2,4</t>
+          <t>-4,37; 2,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-17,5; -0,02</t>
+          <t>-15,96; 0,12</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,47</t>
+          <t>-1,15; 3,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 2,89</t>
+          <t>-1,78; 2,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,39; -3,99</t>
+          <t>-20,09; -3,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,77</t>
+          <t>-0,57; 3,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 3,07</t>
+          <t>-1,09; 3,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 4,23</t>
+          <t>-3,54; 3,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,0</t>
+          <t>-0,01; 3,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,32</t>
+          <t>-0,86; 2,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,12; -0,4</t>
+          <t>-8,49; -0,35</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,82</t>
+          <t>-1,21; 3,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,16</t>
+          <t>-1,89; 2,88</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,6; -4,32</t>
+          <t>-21,28; -3,98</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 4,1</t>
+          <t>-0,59; 4,22</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,36</t>
+          <t>-1,16; 3,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 4,58</t>
+          <t>-3,78; 4,27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,25</t>
+          <t>-0,01; 3,39</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,5</t>
+          <t>-0,9; 2,54</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-9,72; -0,44</t>
+          <t>-9,13; -0,38</t>
         </is>
       </c>
     </row>
